--- a/data_lake/industry/CFM/Index.xlsx
+++ b/data_lake/industry/CFM/Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B6FB0B-1E0C-4A58-9BCE-05B6E62E13FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900A01C9-6400-4A44-AD7F-FDFE92E354DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18100" yWindow="820" windowWidth="17900" windowHeight="20660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -419,30 +419,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -463,7 +463,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -471,7 +471,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -508,7 +508,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -519,10 +519,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -534,33 +534,33 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -578,7 +578,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1506,6 +1506,27 @@
                 <c:pt idx="292">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="293">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2393,6 +2414,27 @@
                 </c:pt>
                 <c:pt idx="292">
                   <c:v>4105.1899999999996</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4252.13</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4282.57</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4274.5600000000004</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4274.5600000000004</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4358.7</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4368.28</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>4368.28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3315,6 +3357,27 @@
                 <c:pt idx="292">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="293">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46287</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4202,6 +4265,27 @@
                 </c:pt>
                 <c:pt idx="292">
                   <c:v>2987.73</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>2987.73</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>2987.73</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>2979.67</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>2980.03</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>2973.83</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>2968.31</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>2967.62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5278,20 +5362,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y294"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y301"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.69921875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="11.69921875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="11.69921875" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.59765625" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.59765625" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.6640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="14" customWidth="1"/>
+    <col min="5" max="6" width="11.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="17"/>
     <col min="26" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>114</v>
       </c>
@@ -5330,7 +5413,7 @@
       <c r="X1" s="10"/>
       <c r="Y1" s="10"/>
     </row>
-    <row r="2" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>44096</v>
       </c>
@@ -5369,7 +5452,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>44103</v>
       </c>
@@ -5408,7 +5491,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>44117</v>
       </c>
@@ -5447,7 +5530,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>44124</v>
       </c>
@@ -5486,7 +5569,7 @@
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
     </row>
-    <row r="6" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>44131</v>
       </c>
@@ -5525,7 +5608,7 @@
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
     </row>
-    <row r="7" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>44138</v>
       </c>
@@ -5564,7 +5647,7 @@
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
     </row>
-    <row r="8" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>44145</v>
       </c>
@@ -5603,7 +5686,7 @@
       <c r="X8" s="10"/>
       <c r="Y8" s="10"/>
     </row>
-    <row r="9" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>44152</v>
       </c>
@@ -5642,7 +5725,7 @@
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
     </row>
-    <row r="10" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>44159</v>
       </c>
@@ -5681,7 +5764,7 @@
       <c r="X10" s="10"/>
       <c r="Y10" s="10"/>
     </row>
-    <row r="11" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>44166</v>
       </c>
@@ -5720,7 +5803,7 @@
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
     </row>
-    <row r="12" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>44173</v>
       </c>
@@ -5759,7 +5842,7 @@
       <c r="X12" s="10"/>
       <c r="Y12" s="10"/>
     </row>
-    <row r="13" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>44180</v>
       </c>
@@ -5798,7 +5881,7 @@
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
     </row>
-    <row r="14" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>44187</v>
       </c>
@@ -5837,7 +5920,7 @@
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
     </row>
-    <row r="15" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>44194</v>
       </c>
@@ -5876,7 +5959,7 @@
       <c r="X15" s="10"/>
       <c r="Y15" s="10"/>
     </row>
-    <row r="16" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>44201</v>
       </c>
@@ -5915,7 +5998,7 @@
       <c r="X16" s="10"/>
       <c r="Y16" s="10"/>
     </row>
-    <row r="17" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>44208</v>
       </c>
@@ -5954,7 +6037,7 @@
       <c r="X17" s="10"/>
       <c r="Y17" s="10"/>
     </row>
-    <row r="18" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>44215</v>
       </c>
@@ -5993,7 +6076,7 @@
       <c r="X18" s="10"/>
       <c r="Y18" s="10"/>
     </row>
-    <row r="19" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>44222</v>
       </c>
@@ -6032,7 +6115,7 @@
       <c r="X19" s="10"/>
       <c r="Y19" s="10"/>
     </row>
-    <row r="20" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>44229</v>
       </c>
@@ -6071,7 +6154,7 @@
       <c r="X20" s="10"/>
       <c r="Y20" s="10"/>
     </row>
-    <row r="21" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>44236</v>
       </c>
@@ -6110,7 +6193,7 @@
       <c r="X21" s="10"/>
       <c r="Y21" s="10"/>
     </row>
-    <row r="22" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>44250</v>
       </c>
@@ -6149,7 +6232,7 @@
       <c r="X22" s="10"/>
       <c r="Y22" s="10"/>
     </row>
-    <row r="23" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>44257</v>
       </c>
@@ -6188,7 +6271,7 @@
       <c r="X23" s="10"/>
       <c r="Y23" s="10"/>
     </row>
-    <row r="24" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>44264</v>
       </c>
@@ -6227,7 +6310,7 @@
       <c r="X24" s="10"/>
       <c r="Y24" s="10"/>
     </row>
-    <row r="25" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>44271</v>
       </c>
@@ -6266,7 +6349,7 @@
       <c r="X25" s="10"/>
       <c r="Y25" s="10"/>
     </row>
-    <row r="26" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>44278</v>
       </c>
@@ -6305,7 +6388,7 @@
       <c r="X26" s="10"/>
       <c r="Y26" s="10"/>
     </row>
-    <row r="27" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>44285</v>
       </c>
@@ -6344,7 +6427,7 @@
       <c r="X27" s="10"/>
       <c r="Y27" s="10"/>
     </row>
-    <row r="28" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>44292</v>
       </c>
@@ -6383,7 +6466,7 @@
       <c r="X28" s="10"/>
       <c r="Y28" s="10"/>
     </row>
-    <row r="29" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>44299</v>
       </c>
@@ -6422,7 +6505,7 @@
       <c r="X29" s="10"/>
       <c r="Y29" s="10"/>
     </row>
-    <row r="30" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>44306</v>
       </c>
@@ -6461,7 +6544,7 @@
       <c r="X30" s="10"/>
       <c r="Y30" s="10"/>
     </row>
-    <row r="31" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>44313</v>
       </c>
@@ -6500,7 +6583,7 @@
       <c r="X31" s="10"/>
       <c r="Y31" s="10"/>
     </row>
-    <row r="32" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>44322</v>
       </c>
@@ -6539,7 +6622,7 @@
       <c r="X32" s="10"/>
       <c r="Y32" s="10"/>
     </row>
-    <row r="33" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>44327</v>
       </c>
@@ -6578,7 +6661,7 @@
       <c r="X33" s="10"/>
       <c r="Y33" s="10"/>
     </row>
-    <row r="34" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>44334</v>
       </c>
@@ -6617,7 +6700,7 @@
       <c r="X34" s="10"/>
       <c r="Y34" s="10"/>
     </row>
-    <row r="35" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>44341</v>
       </c>
@@ -6656,7 +6739,7 @@
       <c r="X35" s="10"/>
       <c r="Y35" s="10"/>
     </row>
-    <row r="36" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>44348</v>
       </c>
@@ -6695,7 +6778,7 @@
       <c r="X36" s="10"/>
       <c r="Y36" s="10"/>
     </row>
-    <row r="37" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>44355</v>
       </c>
@@ -6734,7 +6817,7 @@
       <c r="X37" s="10"/>
       <c r="Y37" s="10"/>
     </row>
-    <row r="38" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>44362</v>
       </c>
@@ -6773,7 +6856,7 @@
       <c r="X38" s="10"/>
       <c r="Y38" s="10"/>
     </row>
-    <row r="39" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>44369</v>
       </c>
@@ -6812,7 +6895,7 @@
       <c r="X39" s="10"/>
       <c r="Y39" s="10"/>
     </row>
-    <row r="40" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>44376</v>
       </c>
@@ -6851,7 +6934,7 @@
       <c r="X40" s="10"/>
       <c r="Y40" s="10"/>
     </row>
-    <row r="41" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>44383</v>
       </c>
@@ -6890,7 +6973,7 @@
       <c r="X41" s="10"/>
       <c r="Y41" s="10"/>
     </row>
-    <row r="42" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>44390</v>
       </c>
@@ -6929,7 +7012,7 @@
       <c r="X42" s="10"/>
       <c r="Y42" s="10"/>
     </row>
-    <row r="43" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>44397</v>
       </c>
@@ -6968,7 +7051,7 @@
       <c r="X43" s="10"/>
       <c r="Y43" s="10"/>
     </row>
-    <row r="44" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>44404</v>
       </c>
@@ -7007,7 +7090,7 @@
       <c r="X44" s="10"/>
       <c r="Y44" s="10"/>
     </row>
-    <row r="45" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>44411</v>
       </c>
@@ -7046,7 +7129,7 @@
       <c r="X45" s="10"/>
       <c r="Y45" s="10"/>
     </row>
-    <row r="46" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>44418</v>
       </c>
@@ -7085,7 +7168,7 @@
       <c r="X46" s="10"/>
       <c r="Y46" s="10"/>
     </row>
-    <row r="47" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>44425</v>
       </c>
@@ -7124,7 +7207,7 @@
       <c r="X47" s="10"/>
       <c r="Y47" s="10"/>
     </row>
-    <row r="48" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>44432</v>
       </c>
@@ -7163,7 +7246,7 @@
       <c r="X48" s="10"/>
       <c r="Y48" s="10"/>
     </row>
-    <row r="49" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>44439</v>
       </c>
@@ -7202,7 +7285,7 @@
       <c r="X49" s="10"/>
       <c r="Y49" s="10"/>
     </row>
-    <row r="50" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>44446</v>
       </c>
@@ -7241,7 +7324,7 @@
       <c r="X50" s="10"/>
       <c r="Y50" s="10"/>
     </row>
-    <row r="51" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>44453</v>
       </c>
@@ -7280,7 +7363,7 @@
       <c r="X51" s="10"/>
       <c r="Y51" s="10"/>
     </row>
-    <row r="52" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>44461</v>
       </c>
@@ -7319,7 +7402,7 @@
       <c r="X52" s="10"/>
       <c r="Y52" s="10"/>
     </row>
-    <row r="53" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>44467</v>
       </c>
@@ -7358,7 +7441,7 @@
       <c r="X53" s="10"/>
       <c r="Y53" s="10"/>
     </row>
-    <row r="54" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>44481</v>
       </c>
@@ -7397,7 +7480,7 @@
       <c r="X54" s="10"/>
       <c r="Y54" s="10"/>
     </row>
-    <row r="55" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>44488</v>
       </c>
@@ -7436,7 +7519,7 @@
       <c r="X55" s="10"/>
       <c r="Y55" s="10"/>
     </row>
-    <row r="56" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>44495</v>
       </c>
@@ -7475,7 +7558,7 @@
       <c r="X56" s="10"/>
       <c r="Y56" s="10"/>
     </row>
-    <row r="57" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>44502</v>
       </c>
@@ -7514,7 +7597,7 @@
       <c r="X57" s="10"/>
       <c r="Y57" s="10"/>
     </row>
-    <row r="58" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>44509</v>
       </c>
@@ -7553,7 +7636,7 @@
       <c r="X58" s="10"/>
       <c r="Y58" s="10"/>
     </row>
-    <row r="59" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>44516</v>
       </c>
@@ -7592,7 +7675,7 @@
       <c r="X59" s="10"/>
       <c r="Y59" s="10"/>
     </row>
-    <row r="60" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>44523</v>
       </c>
@@ -7631,7 +7714,7 @@
       <c r="X60" s="10"/>
       <c r="Y60" s="10"/>
     </row>
-    <row r="61" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>44530</v>
       </c>
@@ -7670,7 +7753,7 @@
       <c r="X61" s="10"/>
       <c r="Y61" s="10"/>
     </row>
-    <row r="62" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>44537</v>
       </c>
@@ -7709,7 +7792,7 @@
       <c r="X62" s="10"/>
       <c r="Y62" s="10"/>
     </row>
-    <row r="63" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>44544</v>
       </c>
@@ -7748,7 +7831,7 @@
       <c r="X63" s="10"/>
       <c r="Y63" s="10"/>
     </row>
-    <row r="64" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>44551</v>
       </c>
@@ -7787,7 +7870,7 @@
       <c r="X64" s="10"/>
       <c r="Y64" s="10"/>
     </row>
-    <row r="65" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>44558</v>
       </c>
@@ -7826,7 +7909,7 @@
       <c r="X65" s="10"/>
       <c r="Y65" s="10"/>
     </row>
-    <row r="66" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>44565</v>
       </c>
@@ -7865,7 +7948,7 @@
       <c r="X66" s="10"/>
       <c r="Y66" s="10"/>
     </row>
-    <row r="67" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>44572</v>
       </c>
@@ -7904,7 +7987,7 @@
       <c r="X67" s="10"/>
       <c r="Y67" s="10"/>
     </row>
-    <row r="68" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>44579</v>
       </c>
@@ -7943,7 +8026,7 @@
       <c r="X68" s="10"/>
       <c r="Y68" s="10"/>
     </row>
-    <row r="69" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>44586</v>
       </c>
@@ -7982,7 +8065,7 @@
       <c r="X69" s="10"/>
       <c r="Y69" s="10"/>
     </row>
-    <row r="70" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>44600</v>
       </c>
@@ -8021,7 +8104,7 @@
       <c r="X70" s="10"/>
       <c r="Y70" s="10"/>
     </row>
-    <row r="71" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>44607</v>
       </c>
@@ -8060,7 +8143,7 @@
       <c r="X71" s="10"/>
       <c r="Y71" s="10"/>
     </row>
-    <row r="72" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>44614</v>
       </c>
@@ -8099,7 +8182,7 @@
       <c r="X72" s="10"/>
       <c r="Y72" s="10"/>
     </row>
-    <row r="73" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>44621</v>
       </c>
@@ -8138,7 +8221,7 @@
       <c r="X73" s="10"/>
       <c r="Y73" s="10"/>
     </row>
-    <row r="74" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>44628</v>
       </c>
@@ -8177,7 +8260,7 @@
       <c r="X74" s="10"/>
       <c r="Y74" s="10"/>
     </row>
-    <row r="75" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>44635</v>
       </c>
@@ -8216,7 +8299,7 @@
       <c r="X75" s="10"/>
       <c r="Y75" s="10"/>
     </row>
-    <row r="76" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>44642</v>
       </c>
@@ -8255,7 +8338,7 @@
       <c r="X76" s="10"/>
       <c r="Y76" s="10"/>
     </row>
-    <row r="77" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>44649</v>
       </c>
@@ -8294,7 +8377,7 @@
       <c r="X77" s="10"/>
       <c r="Y77" s="10"/>
     </row>
-    <row r="78" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>44657</v>
       </c>
@@ -8333,7 +8416,7 @@
       <c r="X78" s="10"/>
       <c r="Y78" s="10"/>
     </row>
-    <row r="79" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>44663</v>
       </c>
@@ -8372,7 +8455,7 @@
       <c r="X79" s="10"/>
       <c r="Y79" s="10"/>
     </row>
-    <row r="80" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>44670</v>
       </c>
@@ -8411,7 +8494,7 @@
       <c r="X80" s="10"/>
       <c r="Y80" s="10"/>
     </row>
-    <row r="81" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>44677</v>
       </c>
@@ -8450,7 +8533,7 @@
       <c r="X81" s="10"/>
       <c r="Y81" s="10"/>
     </row>
-    <row r="82" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>44686</v>
       </c>
@@ -8489,7 +8572,7 @@
       <c r="X82" s="10"/>
       <c r="Y82" s="10"/>
     </row>
-    <row r="83" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>44691</v>
       </c>
@@ -8528,7 +8611,7 @@
       <c r="X83" s="10"/>
       <c r="Y83" s="10"/>
     </row>
-    <row r="84" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>44698</v>
       </c>
@@ -8567,7 +8650,7 @@
       <c r="X84" s="10"/>
       <c r="Y84" s="10"/>
     </row>
-    <row r="85" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>44705</v>
       </c>
@@ -8606,7 +8689,7 @@
       <c r="X85" s="10"/>
       <c r="Y85" s="10"/>
     </row>
-    <row r="86" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>44712</v>
       </c>
@@ -8645,7 +8728,7 @@
       <c r="X86" s="10"/>
       <c r="Y86" s="10"/>
     </row>
-    <row r="87" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>44719</v>
       </c>
@@ -8684,7 +8767,7 @@
       <c r="X87" s="10"/>
       <c r="Y87" s="10"/>
     </row>
-    <row r="88" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>44726</v>
       </c>
@@ -8723,7 +8806,7 @@
       <c r="X88" s="10"/>
       <c r="Y88" s="10"/>
     </row>
-    <row r="89" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>44733</v>
       </c>
@@ -8762,7 +8845,7 @@
       <c r="X89" s="10"/>
       <c r="Y89" s="10"/>
     </row>
-    <row r="90" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>44740</v>
       </c>
@@ -8801,7 +8884,7 @@
       <c r="X90" s="10"/>
       <c r="Y90" s="10"/>
     </row>
-    <row r="91" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>44747</v>
       </c>
@@ -8840,7 +8923,7 @@
       <c r="X91" s="10"/>
       <c r="Y91" s="10"/>
     </row>
-    <row r="92" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>44754</v>
       </c>
@@ -8879,7 +8962,7 @@
       <c r="X92" s="10"/>
       <c r="Y92" s="10"/>
     </row>
-    <row r="93" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>44761</v>
       </c>
@@ -8918,7 +9001,7 @@
       <c r="X93" s="10"/>
       <c r="Y93" s="10"/>
     </row>
-    <row r="94" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>44768</v>
       </c>
@@ -8957,7 +9040,7 @@
       <c r="X94" s="10"/>
       <c r="Y94" s="10"/>
     </row>
-    <row r="95" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>44775</v>
       </c>
@@ -8996,7 +9079,7 @@
       <c r="X95" s="10"/>
       <c r="Y95" s="10"/>
     </row>
-    <row r="96" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>44782</v>
       </c>
@@ -9035,7 +9118,7 @@
       <c r="X96" s="10"/>
       <c r="Y96" s="10"/>
     </row>
-    <row r="97" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>44789</v>
       </c>
@@ -9074,7 +9157,7 @@
       <c r="X97" s="10"/>
       <c r="Y97" s="10"/>
     </row>
-    <row r="98" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>44796</v>
       </c>
@@ -9113,7 +9196,7 @@
       <c r="X98" s="10"/>
       <c r="Y98" s="10"/>
     </row>
-    <row r="99" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>44803</v>
       </c>
@@ -9152,7 +9235,7 @@
       <c r="X99" s="10"/>
       <c r="Y99" s="10"/>
     </row>
-    <row r="100" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>44810</v>
       </c>
@@ -9191,7 +9274,7 @@
       <c r="X100" s="10"/>
       <c r="Y100" s="10"/>
     </row>
-    <row r="101" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>44817</v>
       </c>
@@ -9230,7 +9313,7 @@
       <c r="X101" s="10"/>
       <c r="Y101" s="10"/>
     </row>
-    <row r="102" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>44824</v>
       </c>
@@ -9269,7 +9352,7 @@
       <c r="X102" s="10"/>
       <c r="Y102" s="10"/>
     </row>
-    <row r="103" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>44831</v>
       </c>
@@ -9308,7 +9391,7 @@
       <c r="X103" s="10"/>
       <c r="Y103" s="10"/>
     </row>
-    <row r="104" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>44845</v>
       </c>
@@ -9347,7 +9430,7 @@
       <c r="X104" s="10"/>
       <c r="Y104" s="10"/>
     </row>
-    <row r="105" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>44852</v>
       </c>
@@ -9386,7 +9469,7 @@
       <c r="X105" s="10"/>
       <c r="Y105" s="10"/>
     </row>
-    <row r="106" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>44859</v>
       </c>
@@ -9425,7 +9508,7 @@
       <c r="X106" s="10"/>
       <c r="Y106" s="10"/>
     </row>
-    <row r="107" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>44866</v>
       </c>
@@ -9464,7 +9547,7 @@
       <c r="X107" s="10"/>
       <c r="Y107" s="10"/>
     </row>
-    <row r="108" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>44873</v>
       </c>
@@ -9503,7 +9586,7 @@
       <c r="X108" s="10"/>
       <c r="Y108" s="10"/>
     </row>
-    <row r="109" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>44880</v>
       </c>
@@ -9542,7 +9625,7 @@
       <c r="X109" s="10"/>
       <c r="Y109" s="10"/>
     </row>
-    <row r="110" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>44887</v>
       </c>
@@ -9581,7 +9664,7 @@
       <c r="X110" s="10"/>
       <c r="Y110" s="10"/>
     </row>
-    <row r="111" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>44894</v>
       </c>
@@ -9620,7 +9703,7 @@
       <c r="X111" s="10"/>
       <c r="Y111" s="10"/>
     </row>
-    <row r="112" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>44901</v>
       </c>
@@ -9659,7 +9742,7 @@
       <c r="X112" s="10"/>
       <c r="Y112" s="10"/>
     </row>
-    <row r="113" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>44908</v>
       </c>
@@ -9698,7 +9781,7 @@
       <c r="X113" s="10"/>
       <c r="Y113" s="10"/>
     </row>
-    <row r="114" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>44915</v>
       </c>
@@ -9737,7 +9820,7 @@
       <c r="X114" s="10"/>
       <c r="Y114" s="10"/>
     </row>
-    <row r="115" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>44922</v>
       </c>
@@ -9776,7 +9859,7 @@
       <c r="X115" s="10"/>
       <c r="Y115" s="10"/>
     </row>
-    <row r="116" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>44929</v>
       </c>
@@ -9815,7 +9898,7 @@
       <c r="X116" s="10"/>
       <c r="Y116" s="10"/>
     </row>
-    <row r="117" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>44936</v>
       </c>
@@ -9854,7 +9937,7 @@
       <c r="X117" s="10"/>
       <c r="Y117" s="10"/>
     </row>
-    <row r="118" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>44943</v>
       </c>
@@ -9893,7 +9976,7 @@
       <c r="X118" s="10"/>
       <c r="Y118" s="10"/>
     </row>
-    <row r="119" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>44957</v>
       </c>
@@ -9932,7 +10015,7 @@
       <c r="X119" s="10"/>
       <c r="Y119" s="10"/>
     </row>
-    <row r="120" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>44964</v>
       </c>
@@ -9971,7 +10054,7 @@
       <c r="X120" s="10"/>
       <c r="Y120" s="10"/>
     </row>
-    <row r="121" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>44971</v>
       </c>
@@ -10010,7 +10093,7 @@
       <c r="X121" s="10"/>
       <c r="Y121" s="10"/>
     </row>
-    <row r="122" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>44978</v>
       </c>
@@ -10049,7 +10132,7 @@
       <c r="X122" s="10"/>
       <c r="Y122" s="10"/>
     </row>
-    <row r="123" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>44985</v>
       </c>
@@ -10088,7 +10171,7 @@
       <c r="X123" s="10"/>
       <c r="Y123" s="10"/>
     </row>
-    <row r="124" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>44992</v>
       </c>
@@ -10127,7 +10210,7 @@
       <c r="X124" s="10"/>
       <c r="Y124" s="10"/>
     </row>
-    <row r="125" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>44999</v>
       </c>
@@ -10166,7 +10249,7 @@
       <c r="X125" s="10"/>
       <c r="Y125" s="10"/>
     </row>
-    <row r="126" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>45006</v>
       </c>
@@ -10205,7 +10288,7 @@
       <c r="X126" s="10"/>
       <c r="Y126" s="10"/>
     </row>
-    <row r="127" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>45013</v>
       </c>
@@ -10244,7 +10327,7 @@
       <c r="X127" s="10"/>
       <c r="Y127" s="10"/>
     </row>
-    <row r="128" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>45020</v>
       </c>
@@ -10283,7 +10366,7 @@
       <c r="X128" s="10"/>
       <c r="Y128" s="10"/>
     </row>
-    <row r="129" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>45027</v>
       </c>
@@ -10322,7 +10405,7 @@
       <c r="X129" s="10"/>
       <c r="Y129" s="10"/>
     </row>
-    <row r="130" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>45034</v>
       </c>
@@ -10361,7 +10444,7 @@
       <c r="X130" s="10"/>
       <c r="Y130" s="10"/>
     </row>
-    <row r="131" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>45041</v>
       </c>
@@ -10400,7 +10483,7 @@
       <c r="X131" s="10"/>
       <c r="Y131" s="10"/>
     </row>
-    <row r="132" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>45050</v>
       </c>
@@ -10439,7 +10522,7 @@
       <c r="X132" s="10"/>
       <c r="Y132" s="10"/>
     </row>
-    <row r="133" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>45055</v>
       </c>
@@ -10478,7 +10561,7 @@
       <c r="X133" s="10"/>
       <c r="Y133" s="10"/>
     </row>
-    <row r="134" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>45062</v>
       </c>
@@ -10517,7 +10600,7 @@
       <c r="X134" s="10"/>
       <c r="Y134" s="10"/>
     </row>
-    <row r="135" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>45069</v>
       </c>
@@ -10556,7 +10639,7 @@
       <c r="X135" s="10"/>
       <c r="Y135" s="10"/>
     </row>
-    <row r="136" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>45076</v>
       </c>
@@ -10595,7 +10678,7 @@
       <c r="X136" s="10"/>
       <c r="Y136" s="10"/>
     </row>
-    <row r="137" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>45083</v>
       </c>
@@ -10634,7 +10717,7 @@
       <c r="X137" s="10"/>
       <c r="Y137" s="10"/>
     </row>
-    <row r="138" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>45090</v>
       </c>
@@ -10673,7 +10756,7 @@
       <c r="X138" s="10"/>
       <c r="Y138" s="10"/>
     </row>
-    <row r="139" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>45097</v>
       </c>
@@ -10712,7 +10795,7 @@
       <c r="X139" s="10"/>
       <c r="Y139" s="10"/>
     </row>
-    <row r="140" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>45104</v>
       </c>
@@ -10751,7 +10834,7 @@
       <c r="X140" s="10"/>
       <c r="Y140" s="10"/>
     </row>
-    <row r="141" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>45111</v>
       </c>
@@ -10790,7 +10873,7 @@
       <c r="X141" s="10"/>
       <c r="Y141" s="10"/>
     </row>
-    <row r="142" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>45118</v>
       </c>
@@ -10829,7 +10912,7 @@
       <c r="X142" s="10"/>
       <c r="Y142" s="10"/>
     </row>
-    <row r="143" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>45125</v>
       </c>
@@ -10868,7 +10951,7 @@
       <c r="X143" s="10"/>
       <c r="Y143" s="10"/>
     </row>
-    <row r="144" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>45132</v>
       </c>
@@ -10907,7 +10990,7 @@
       <c r="X144" s="10"/>
       <c r="Y144" s="10"/>
     </row>
-    <row r="145" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>45139</v>
       </c>
@@ -10946,7 +11029,7 @@
       <c r="X145" s="10"/>
       <c r="Y145" s="10"/>
     </row>
-    <row r="146" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>45146</v>
       </c>
@@ -10985,7 +11068,7 @@
       <c r="X146" s="10"/>
       <c r="Y146" s="10"/>
     </row>
-    <row r="147" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>45153</v>
       </c>
@@ -11024,7 +11107,7 @@
       <c r="X147" s="10"/>
       <c r="Y147" s="10"/>
     </row>
-    <row r="148" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>45160</v>
       </c>
@@ -11063,7 +11146,7 @@
       <c r="X148" s="10"/>
       <c r="Y148" s="10"/>
     </row>
-    <row r="149" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>45167</v>
       </c>
@@ -11102,7 +11185,7 @@
       <c r="X149" s="10"/>
       <c r="Y149" s="10"/>
     </row>
-    <row r="150" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>45174</v>
       </c>
@@ -11141,7 +11224,7 @@
       <c r="X150" s="10"/>
       <c r="Y150" s="10"/>
     </row>
-    <row r="151" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>45181</v>
       </c>
@@ -11180,7 +11263,7 @@
       <c r="X151" s="10"/>
       <c r="Y151" s="10"/>
     </row>
-    <row r="152" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>45188</v>
       </c>
@@ -11219,7 +11302,7 @@
       <c r="X152" s="10"/>
       <c r="Y152" s="10"/>
     </row>
-    <row r="153" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>45195</v>
       </c>
@@ -11258,7 +11341,7 @@
       <c r="X153" s="10"/>
       <c r="Y153" s="10"/>
     </row>
-    <row r="154" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>45209</v>
       </c>
@@ -11297,7 +11380,7 @@
       <c r="X154" s="10"/>
       <c r="Y154" s="10"/>
     </row>
-    <row r="155" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>45216</v>
       </c>
@@ -11336,7 +11419,7 @@
       <c r="X155" s="10"/>
       <c r="Y155" s="10"/>
     </row>
-    <row r="156" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>45223</v>
       </c>
@@ -11375,7 +11458,7 @@
       <c r="X156" s="10"/>
       <c r="Y156" s="10"/>
     </row>
-    <row r="157" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>45230</v>
       </c>
@@ -11414,7 +11497,7 @@
       <c r="X157" s="10"/>
       <c r="Y157" s="10"/>
     </row>
-    <row r="158" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>45237</v>
       </c>
@@ -11453,7 +11536,7 @@
       <c r="X158" s="10"/>
       <c r="Y158" s="10"/>
     </row>
-    <row r="159" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>45244</v>
       </c>
@@ -11492,7 +11575,7 @@
       <c r="X159" s="10"/>
       <c r="Y159" s="10"/>
     </row>
-    <row r="160" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>45251</v>
       </c>
@@ -11531,7 +11614,7 @@
       <c r="X160" s="10"/>
       <c r="Y160" s="10"/>
     </row>
-    <row r="161" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>45258</v>
       </c>
@@ -11570,7 +11653,7 @@
       <c r="X161" s="10"/>
       <c r="Y161" s="10"/>
     </row>
-    <row r="162" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>45265</v>
       </c>
@@ -11609,7 +11692,7 @@
       <c r="X162" s="10"/>
       <c r="Y162" s="10"/>
     </row>
-    <row r="163" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>45272</v>
       </c>
@@ -11648,7 +11731,7 @@
       <c r="X163" s="10"/>
       <c r="Y163" s="10"/>
     </row>
-    <row r="164" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>45279</v>
       </c>
@@ -11687,7 +11770,7 @@
       <c r="X164" s="10"/>
       <c r="Y164" s="10"/>
     </row>
-    <row r="165" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>45286</v>
       </c>
@@ -11726,7 +11809,7 @@
       <c r="X165" s="10"/>
       <c r="Y165" s="10"/>
     </row>
-    <row r="166" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>45293</v>
       </c>
@@ -11765,7 +11848,7 @@
       <c r="X166" s="10"/>
       <c r="Y166" s="10"/>
     </row>
-    <row r="167" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>45300</v>
       </c>
@@ -11804,7 +11887,7 @@
       <c r="X167" s="10"/>
       <c r="Y167" s="10"/>
     </row>
-    <row r="168" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>45307</v>
       </c>
@@ -11843,7 +11926,7 @@
       <c r="X168" s="10"/>
       <c r="Y168" s="10"/>
     </row>
-    <row r="169" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>45314</v>
       </c>
@@ -11882,7 +11965,7 @@
       <c r="X169" s="10"/>
       <c r="Y169" s="10"/>
     </row>
-    <row r="170" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A170" s="12">
         <v>45321</v>
       </c>
@@ -11921,7 +12004,7 @@
       <c r="X170" s="10"/>
       <c r="Y170" s="10"/>
     </row>
-    <row r="171" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>45328</v>
       </c>
@@ -11960,7 +12043,7 @@
       <c r="X171" s="10"/>
       <c r="Y171" s="10"/>
     </row>
-    <row r="172" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A172" s="12">
         <v>45342</v>
       </c>
@@ -11999,7 +12082,7 @@
       <c r="X172" s="10"/>
       <c r="Y172" s="10"/>
     </row>
-    <row r="173" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A173" s="12">
         <v>45349</v>
       </c>
@@ -12038,7 +12121,7 @@
       <c r="X173" s="10"/>
       <c r="Y173" s="10"/>
     </row>
-    <row r="174" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A174" s="12">
         <v>45356</v>
       </c>
@@ -12077,7 +12160,7 @@
       <c r="X174" s="10"/>
       <c r="Y174" s="10"/>
     </row>
-    <row r="175" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="12">
         <v>45363</v>
       </c>
@@ -12116,7 +12199,7 @@
       <c r="X175" s="10"/>
       <c r="Y175" s="10"/>
     </row>
-    <row r="176" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A176" s="12">
         <v>45370</v>
       </c>
@@ -12155,7 +12238,7 @@
       <c r="X176" s="10"/>
       <c r="Y176" s="10"/>
     </row>
-    <row r="177" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A177" s="12">
         <v>45377</v>
       </c>
@@ -12194,7 +12277,7 @@
       <c r="X177" s="10"/>
       <c r="Y177" s="10"/>
     </row>
-    <row r="178" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A178" s="12">
         <v>45384</v>
       </c>
@@ -12233,7 +12316,7 @@
       <c r="X178" s="10"/>
       <c r="Y178" s="10"/>
     </row>
-    <row r="179" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A179" s="12">
         <v>45391</v>
       </c>
@@ -12272,7 +12355,7 @@
       <c r="X179" s="10"/>
       <c r="Y179" s="10"/>
     </row>
-    <row r="180" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A180" s="12">
         <v>45398</v>
       </c>
@@ -12311,7 +12394,7 @@
       <c r="X180" s="10"/>
       <c r="Y180" s="10"/>
     </row>
-    <row r="181" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A181" s="12">
         <v>45405</v>
       </c>
@@ -12350,7 +12433,7 @@
       <c r="X181" s="10"/>
       <c r="Y181" s="10"/>
     </row>
-    <row r="182" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A182" s="12">
         <v>45412</v>
       </c>
@@ -12389,7 +12472,7 @@
       <c r="X182" s="10"/>
       <c r="Y182" s="10"/>
     </row>
-    <row r="183" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A183" s="12">
         <v>45419</v>
       </c>
@@ -12428,7 +12511,7 @@
       <c r="X183" s="10"/>
       <c r="Y183" s="10"/>
     </row>
-    <row r="184" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A184" s="12">
         <v>45426</v>
       </c>
@@ -12467,7 +12550,7 @@
       <c r="X184" s="10"/>
       <c r="Y184" s="10"/>
     </row>
-    <row r="185" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="12">
         <v>45433</v>
       </c>
@@ -12506,7 +12589,7 @@
       <c r="X185" s="10"/>
       <c r="Y185" s="10"/>
     </row>
-    <row r="186" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A186" s="12">
         <v>45440</v>
       </c>
@@ -12545,7 +12628,7 @@
       <c r="X186" s="10"/>
       <c r="Y186" s="10"/>
     </row>
-    <row r="187" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="12">
         <v>45447</v>
       </c>
@@ -12584,7 +12667,7 @@
       <c r="X187" s="10"/>
       <c r="Y187" s="10"/>
     </row>
-    <row r="188" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A188" s="12">
         <v>45454</v>
       </c>
@@ -12623,7 +12706,7 @@
       <c r="X188" s="10"/>
       <c r="Y188" s="10"/>
     </row>
-    <row r="189" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A189" s="12">
         <v>45461</v>
       </c>
@@ -12662,7 +12745,7 @@
       <c r="X189" s="10"/>
       <c r="Y189" s="10"/>
     </row>
-    <row r="190" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="12">
         <v>45468</v>
       </c>
@@ -12701,7 +12784,7 @@
       <c r="X190" s="10"/>
       <c r="Y190" s="10"/>
     </row>
-    <row r="191" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A191" s="12">
         <v>45475</v>
       </c>
@@ -12740,7 +12823,7 @@
       <c r="X191" s="10"/>
       <c r="Y191" s="10"/>
     </row>
-    <row r="192" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A192" s="12">
         <v>45482</v>
       </c>
@@ -12779,7 +12862,7 @@
       <c r="X192" s="10"/>
       <c r="Y192" s="10"/>
     </row>
-    <row r="193" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A193" s="12">
         <v>45489</v>
       </c>
@@ -12818,7 +12901,7 @@
       <c r="X193" s="10"/>
       <c r="Y193" s="10"/>
     </row>
-    <row r="194" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A194" s="12">
         <v>45496</v>
       </c>
@@ -12857,7 +12940,7 @@
       <c r="X194" s="10"/>
       <c r="Y194" s="10"/>
     </row>
-    <row r="195" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A195" s="12">
         <v>45503</v>
       </c>
@@ -12896,7 +12979,7 @@
       <c r="X195" s="10"/>
       <c r="Y195" s="10"/>
     </row>
-    <row r="196" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A196" s="12">
         <v>45510</v>
       </c>
@@ -12935,7 +13018,7 @@
       <c r="X196" s="10"/>
       <c r="Y196" s="10"/>
     </row>
-    <row r="197" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A197" s="12">
         <v>45517</v>
       </c>
@@ -12974,7 +13057,7 @@
       <c r="X197" s="10"/>
       <c r="Y197" s="10"/>
     </row>
-    <row r="198" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A198" s="12">
         <v>45524</v>
       </c>
@@ -13013,7 +13096,7 @@
       <c r="X198" s="10"/>
       <c r="Y198" s="10"/>
     </row>
-    <row r="199" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A199" s="12">
         <v>45531</v>
       </c>
@@ -13052,7 +13135,7 @@
       <c r="X199" s="10"/>
       <c r="Y199" s="10"/>
     </row>
-    <row r="200" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A200" s="12">
         <v>45538</v>
       </c>
@@ -13091,7 +13174,7 @@
       <c r="X200" s="10"/>
       <c r="Y200" s="10"/>
     </row>
-    <row r="201" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A201" s="12">
         <v>45545</v>
       </c>
@@ -13130,7 +13213,7 @@
       <c r="X201" s="10"/>
       <c r="Y201" s="10"/>
     </row>
-    <row r="202" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A202" s="12">
         <v>45553</v>
       </c>
@@ -13169,7 +13252,7 @@
       <c r="X202" s="10"/>
       <c r="Y202" s="10"/>
     </row>
-    <row r="203" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A203" s="12">
         <v>45559</v>
       </c>
@@ -13208,7 +13291,7 @@
       <c r="X203" s="10"/>
       <c r="Y203" s="10"/>
     </row>
-    <row r="204" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A204" s="12">
         <v>45573</v>
       </c>
@@ -13247,7 +13330,7 @@
       <c r="X204" s="10"/>
       <c r="Y204" s="10"/>
     </row>
-    <row r="205" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A205" s="12">
         <v>45580</v>
       </c>
@@ -13286,7 +13369,7 @@
       <c r="X205" s="10"/>
       <c r="Y205" s="10"/>
     </row>
-    <row r="206" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A206" s="12">
         <v>45587</v>
       </c>
@@ -13325,7 +13408,7 @@
       <c r="X206" s="10"/>
       <c r="Y206" s="10"/>
     </row>
-    <row r="207" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A207" s="12">
         <v>45594</v>
       </c>
@@ -13364,7 +13447,7 @@
       <c r="X207" s="10"/>
       <c r="Y207" s="10"/>
     </row>
-    <row r="208" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A208" s="12">
         <v>45601</v>
       </c>
@@ -13403,7 +13486,7 @@
       <c r="X208" s="10"/>
       <c r="Y208" s="10"/>
     </row>
-    <row r="209" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A209" s="12">
         <v>45608</v>
       </c>
@@ -13442,7 +13525,7 @@
       <c r="X209" s="10"/>
       <c r="Y209" s="10"/>
     </row>
-    <row r="210" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A210" s="12">
         <v>45615</v>
       </c>
@@ -13481,7 +13564,7 @@
       <c r="X210" s="10"/>
       <c r="Y210" s="10"/>
     </row>
-    <row r="211" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A211" s="12">
         <v>45622</v>
       </c>
@@ -13520,7 +13603,7 @@
       <c r="X211" s="10"/>
       <c r="Y211" s="10"/>
     </row>
-    <row r="212" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A212" s="12">
         <v>45629</v>
       </c>
@@ -13559,7 +13642,7 @@
       <c r="X212" s="10"/>
       <c r="Y212" s="10"/>
     </row>
-    <row r="213" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A213" s="12">
         <v>45636</v>
       </c>
@@ -13598,7 +13681,7 @@
       <c r="X213" s="10"/>
       <c r="Y213" s="10"/>
     </row>
-    <row r="214" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A214" s="12">
         <v>45643</v>
       </c>
@@ -13637,7 +13720,7 @@
       <c r="X214" s="10"/>
       <c r="Y214" s="10"/>
     </row>
-    <row r="215" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A215" s="12">
         <v>45650</v>
       </c>
@@ -13676,7 +13759,7 @@
       <c r="X215" s="10"/>
       <c r="Y215" s="10"/>
     </row>
-    <row r="216" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A216" s="12">
         <v>45657</v>
       </c>
@@ -13715,7 +13798,7 @@
       <c r="X216" s="10"/>
       <c r="Y216" s="10"/>
     </row>
-    <row r="217" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A217" s="12">
         <v>45664</v>
       </c>
@@ -13754,7 +13837,7 @@
       <c r="X217" s="10"/>
       <c r="Y217" s="10"/>
     </row>
-    <row r="218" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A218" s="12">
         <v>45671</v>
       </c>
@@ -13793,7 +13876,7 @@
       <c r="X218" s="10"/>
       <c r="Y218" s="10"/>
     </row>
-    <row r="219" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A219" s="12">
         <v>45678</v>
       </c>
@@ -13832,7 +13915,7 @@
       <c r="X219" s="10"/>
       <c r="Y219" s="10"/>
     </row>
-    <row r="220" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A220" s="12">
         <v>45699</v>
       </c>
@@ -13871,7 +13954,7 @@
       <c r="X220" s="10"/>
       <c r="Y220" s="10"/>
     </row>
-    <row r="221" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A221" s="12">
         <v>45706</v>
       </c>
@@ -13910,7 +13993,7 @@
       <c r="X221" s="10"/>
       <c r="Y221" s="10"/>
     </row>
-    <row r="222" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A222" s="12">
         <v>45713</v>
       </c>
@@ -13949,7 +14032,7 @@
       <c r="X222" s="10"/>
       <c r="Y222" s="10"/>
     </row>
-    <row r="223" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A223" s="12">
         <v>45720</v>
       </c>
@@ -13988,7 +14071,7 @@
       <c r="X223" s="10"/>
       <c r="Y223" s="10"/>
     </row>
-    <row r="224" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A224" s="12">
         <v>45727</v>
       </c>
@@ -14027,7 +14110,7 @@
       <c r="X224" s="10"/>
       <c r="Y224" s="10"/>
     </row>
-    <row r="225" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A225" s="12">
         <v>45734</v>
       </c>
@@ -14066,7 +14149,7 @@
       <c r="X225" s="10"/>
       <c r="Y225" s="10"/>
     </row>
-    <row r="226" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A226" s="12">
         <v>45741</v>
       </c>
@@ -14105,7 +14188,7 @@
       <c r="X226" s="10"/>
       <c r="Y226" s="10"/>
     </row>
-    <row r="227" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A227" s="12">
         <v>45748</v>
       </c>
@@ -14144,7 +14227,7 @@
       <c r="X227" s="10"/>
       <c r="Y227" s="10"/>
     </row>
-    <row r="228" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A228" s="12">
         <v>45755</v>
       </c>
@@ -14183,7 +14266,7 @@
       <c r="X228" s="10"/>
       <c r="Y228" s="10"/>
     </row>
-    <row r="229" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A229" s="12">
         <v>45762</v>
       </c>
@@ -14222,7 +14305,7 @@
       <c r="X229" s="10"/>
       <c r="Y229" s="10"/>
     </row>
-    <row r="230" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A230" s="12">
         <v>45769</v>
       </c>
@@ -14261,7 +14344,7 @@
       <c r="X230" s="10"/>
       <c r="Y230" s="10"/>
     </row>
-    <row r="231" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A231" s="12">
         <v>45776</v>
       </c>
@@ -14300,7 +14383,7 @@
       <c r="X231" s="10"/>
       <c r="Y231" s="10"/>
     </row>
-    <row r="232" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A232" s="12">
         <v>45783</v>
       </c>
@@ -14339,7 +14422,7 @@
       <c r="X232" s="10"/>
       <c r="Y232" s="10"/>
     </row>
-    <row r="233" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A233" s="12">
         <v>45790</v>
       </c>
@@ -14378,7 +14461,7 @@
       <c r="X233" s="10"/>
       <c r="Y233" s="10"/>
     </row>
-    <row r="234" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A234" s="12">
         <v>45797</v>
       </c>
@@ -14417,7 +14500,7 @@
       <c r="X234" s="10"/>
       <c r="Y234" s="10"/>
     </row>
-    <row r="235" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A235" s="12">
         <v>45804</v>
       </c>
@@ -14456,7 +14539,7 @@
       <c r="X235" s="10"/>
       <c r="Y235" s="10"/>
     </row>
-    <row r="236" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A236" s="12">
         <v>45811</v>
       </c>
@@ -14495,7 +14578,7 @@
       <c r="X236" s="10"/>
       <c r="Y236" s="10"/>
     </row>
-    <row r="237" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A237" s="12">
         <v>45818</v>
       </c>
@@ -14534,7 +14617,7 @@
       <c r="X237" s="10"/>
       <c r="Y237" s="10"/>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A238" s="12">
         <v>45825</v>
       </c>
@@ -14573,7 +14656,7 @@
       <c r="X238" s="15"/>
       <c r="Y238" s="15"/>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A239" s="12">
         <v>45832</v>
       </c>
@@ -14612,7 +14695,7 @@
       <c r="X239" s="15"/>
       <c r="Y239" s="15"/>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A240" s="12">
         <v>45839</v>
       </c>
@@ -14632,7 +14715,7 @@
         <v>677.73</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" s="12">
         <v>45846</v>
       </c>
@@ -14652,7 +14735,7 @@
         <v>676.06</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" s="12">
         <v>45853</v>
       </c>
@@ -14672,7 +14755,7 @@
         <v>676.1</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" s="12">
         <v>45860</v>
       </c>
@@ -14692,7 +14775,7 @@
         <v>674.57</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" s="12">
         <v>45867</v>
       </c>
@@ -14712,7 +14795,7 @@
         <v>681.42</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="12">
         <v>45874</v>
       </c>
@@ -14732,7 +14815,7 @@
         <v>681.58</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" s="12">
         <v>45881</v>
       </c>
@@ -14752,7 +14835,7 @@
         <v>681.87</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" s="12">
         <v>45888</v>
       </c>
@@ -14772,7 +14855,7 @@
         <v>682.04</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" s="12">
         <v>45895</v>
       </c>
@@ -14792,7 +14875,7 @@
         <v>681.5</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" s="12">
         <v>45902</v>
       </c>
@@ -14812,7 +14895,7 @@
         <v>679.81</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" s="12">
         <v>45909</v>
       </c>
@@ -14832,7 +14915,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" s="12">
         <v>45916</v>
       </c>
@@ -14852,7 +14935,7 @@
         <v>689.45</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" s="12">
         <v>45923</v>
       </c>
@@ -14872,7 +14955,7 @@
         <v>711.44</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" s="12">
         <v>45930</v>
       </c>
@@ -14892,7 +14975,7 @@
         <v>717.66</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" s="12">
         <v>45944</v>
       </c>
@@ -14912,7 +14995,7 @@
         <v>794.72</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" s="12">
         <v>45951</v>
       </c>
@@ -14932,7 +15015,7 @@
         <v>824.91</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" s="12">
         <v>45958</v>
       </c>
@@ -14952,7 +15035,7 @@
         <v>930.72</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" s="12">
         <v>45965</v>
       </c>
@@ -14972,7 +15055,7 @@
         <v>1015.38</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258" s="12">
         <v>45972</v>
       </c>
@@ -14992,7 +15075,7 @@
         <v>1054.43</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259" s="12">
         <v>45979</v>
       </c>
@@ -15012,7 +15095,7 @@
         <v>1217.8800000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260" s="12">
         <v>45986</v>
       </c>
@@ -15032,7 +15115,7 @@
         <v>1438.48</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" s="12">
         <v>45993</v>
       </c>
@@ -15052,7 +15135,7 @@
         <v>1633.81</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" s="12">
         <v>46000</v>
       </c>
@@ -15072,7 +15155,7 @@
         <v>1735.53</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" s="12">
         <v>46007</v>
       </c>
@@ -15092,7 +15175,7 @@
         <v>1742.09</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" s="12">
         <v>46014</v>
       </c>
@@ -15112,7 +15195,7 @@
         <v>1860.57</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" s="12">
         <v>46021</v>
       </c>
@@ -15132,7 +15215,7 @@
         <v>1896.1</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266" s="12">
         <v>46028</v>
       </c>
@@ -15152,7 +15235,7 @@
         <v>1982.64</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267" s="12">
         <v>46035</v>
       </c>
@@ -15172,7 +15255,7 @@
         <v>2011.73</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268" s="12">
         <v>46042</v>
       </c>
@@ -15192,7 +15275,7 @@
         <v>2229.8200000000002</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" s="12">
         <v>46049</v>
       </c>
@@ -15212,7 +15295,7 @@
         <v>2521.86</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270" s="12">
         <v>46056</v>
       </c>
@@ -15232,7 +15315,7 @@
         <v>2567.14</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" s="12">
         <v>46063</v>
       </c>
@@ -15252,7 +15335,7 @@
         <v>2605.37</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" s="12">
         <v>46077</v>
       </c>
@@ -15272,7 +15355,7 @@
         <v>2750.87</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" s="12">
         <v>46084</v>
       </c>
@@ -15292,7 +15375,7 @@
         <v>2901.01</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" s="12">
         <v>46091</v>
       </c>
@@ -15312,7 +15395,7 @@
         <v>3046.26</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" s="12">
         <v>46098</v>
       </c>
@@ -15332,7 +15415,7 @@
         <v>3198.66</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" s="12">
         <v>46105</v>
       </c>
@@ -15352,7 +15435,7 @@
         <v>3229.87</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" s="12">
         <v>46112</v>
       </c>
@@ -15372,7 +15455,7 @@
         <v>3194.62</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" s="12">
         <v>46119</v>
       </c>
@@ -15392,7 +15475,7 @@
         <v>3194.62</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" s="12">
         <v>46126</v>
       </c>
@@ -15412,7 +15495,7 @@
         <v>3164.63</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" s="12">
         <v>46133</v>
       </c>
@@ -15432,7 +15515,7 @@
         <v>3142.68</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" s="12">
         <v>46140</v>
       </c>
@@ -15452,7 +15535,7 @@
         <v>3059.92</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="12">
         <v>46154</v>
       </c>
@@ -15472,7 +15555,7 @@
         <v>3029.7</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" s="12">
         <v>46161</v>
       </c>
@@ -15492,7 +15575,7 @@
         <v>3019.44</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284" s="12">
         <v>46168</v>
       </c>
@@ -15512,7 +15595,7 @@
         <v>3014.54</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285" s="12">
         <v>46175</v>
       </c>
@@ -15532,7 +15615,7 @@
         <v>3014.38</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" s="12">
         <v>46182</v>
       </c>
@@ -15552,7 +15635,7 @@
         <v>3014.38</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" s="12">
         <v>46189</v>
       </c>
@@ -15572,7 +15655,7 @@
         <v>3015.97</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" s="12">
         <v>46196</v>
       </c>
@@ -15592,7 +15675,7 @@
         <v>3010.97</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" s="12">
         <v>46203</v>
       </c>
@@ -15612,7 +15695,7 @@
         <v>2987.19</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" s="12">
         <v>46210</v>
       </c>
@@ -15632,7 +15715,7 @@
         <v>2988.85</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" s="12">
         <v>46217</v>
       </c>
@@ -15652,7 +15735,7 @@
         <v>2991.37</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" s="12">
         <v>46224</v>
       </c>
@@ -15672,7 +15755,7 @@
         <v>2988.98</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" s="12">
         <v>46231</v>
       </c>
@@ -15692,7 +15775,7 @@
         <v>2988.98</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" s="12">
         <v>46238</v>
       </c>
@@ -15710,6 +15793,146 @@
       </c>
       <c r="F294" s="19">
         <v>2987.73</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A295" s="12">
+        <v>46245</v>
+      </c>
+      <c r="B295" s="12">
+        <v>46245</v>
+      </c>
+      <c r="C295" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D295" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E295" s="19">
+        <v>4252.13</v>
+      </c>
+      <c r="F295" s="19">
+        <v>2987.73</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A296" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B296" s="12">
+        <v>46252</v>
+      </c>
+      <c r="C296" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D296" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E296" s="19">
+        <v>4282.57</v>
+      </c>
+      <c r="F296" s="19">
+        <v>2987.73</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A297" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B297" s="12">
+        <v>46259</v>
+      </c>
+      <c r="C297" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D297" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E297" s="19">
+        <v>4274.5600000000004</v>
+      </c>
+      <c r="F297" s="19">
+        <v>2979.67</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A298" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B298" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C298" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D298" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E298" s="19">
+        <v>4274.5600000000004</v>
+      </c>
+      <c r="F298" s="19">
+        <v>2980.03</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A299" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B299" s="12">
+        <v>46273</v>
+      </c>
+      <c r="C299" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D299" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E299" s="19">
+        <v>4358.7</v>
+      </c>
+      <c r="F299" s="19">
+        <v>2973.83</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A300" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B300" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C300" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D300" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E300" s="19">
+        <v>4368.28</v>
+      </c>
+      <c r="F300" s="19">
+        <v>2968.31</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A301" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B301" s="12">
+        <v>46287</v>
+      </c>
+      <c r="C301" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D301" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E301" s="19">
+        <v>4368.28</v>
+      </c>
+      <c r="F301" s="19">
+        <v>2967.62</v>
       </c>
     </row>
   </sheetData>
@@ -15722,20 +15945,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -15746,22 +15969,22 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -15769,42 +15992,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -15812,32 +16035,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.15">
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C19" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -15845,37 +16068,37 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C23" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
@@ -15883,17 +16106,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C29" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -15901,47 +16124,47 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C32" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C33" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C34" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C35" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C36" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C38" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>44</v>
       </c>
@@ -15949,47 +16172,47 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C40" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C41" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C42" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C43" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C44" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C45" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C46" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C47" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B48" s="2" t="s">
         <v>54</v>
       </c>
@@ -15997,27 +16220,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C50" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C51" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C52" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B53" s="2" t="s">
         <v>60</v>
       </c>
@@ -16025,32 +16248,32 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C54" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C55" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C56" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C57" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C58" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
@@ -16058,17 +16281,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C60" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C61" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
@@ -16076,22 +16299,22 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C63" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C64" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C65" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B66" s="2" t="s">
         <v>76</v>
       </c>
@@ -16099,22 +16322,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C67" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C69" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B70" s="2" t="s">
         <v>81</v>
       </c>
@@ -16122,47 +16345,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C71" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C72" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C73" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C74" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C75" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C76" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C77" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C78" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B79" s="2" t="s">
         <v>91</v>
       </c>
@@ -16170,32 +16393,32 @@
         <v>92</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C80" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C81" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C82" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C83" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C84" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B85" s="2" t="s">
         <v>98</v>
       </c>
@@ -16203,47 +16426,47 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C86" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C87" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C88" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C89" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C90" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C91" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C92" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C93" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.15">
       <c r="C94" s="1" t="s">
         <v>108</v>
       </c>
@@ -16260,7 +16483,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF528F66-5C7C-40F6-B437-A79684695F91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
